--- a/25MMS4124-CISCO-US-Attendance Roster_Splunk Intermediate_10th to 12th Dec.xlsx
+++ b/25MMS4124-CISCO-US-Attendance Roster_Splunk Intermediate_10th to 12th Dec.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\VK_GIT\SPLK_CISCO_10_12_2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1887EE79-3063-41BE-95DE-7B9E945D3FA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B5FC495-8B8B-4526-9620-945C48B607E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -570,12 +570,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -588,6 +582,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -878,10 +878,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="34"/>
+      <c r="C1" s="40"/>
       <c r="D1" s="12"/>
     </row>
     <row r="2" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
@@ -1124,189 +1124,189 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="33" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B5" s="36" t="s">
+      <c r="B5" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="36" t="s">
+      <c r="C5" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="40" t="s">
+      <c r="D5" s="38" t="s">
         <v>46</v>
       </c>
-      <c r="E5" s="40" t="s">
+      <c r="E5" s="38" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B6" s="38" t="s">
+      <c r="B6" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="38" t="s">
+      <c r="C6" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="37" t="s">
+      <c r="D6" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="E6" s="37" t="s">
+      <c r="E6" s="35" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B7" s="39" t="s">
+      <c r="B7" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="39" t="s">
+      <c r="C7" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="37" t="s">
+      <c r="D7" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="37" t="s">
+      <c r="E7" s="35" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="39" t="s">
+      <c r="B8" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="39" t="s">
+      <c r="C8" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="37" t="s">
+      <c r="D8" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="37" t="s">
+      <c r="E8" s="35" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="39" t="s">
+      <c r="B9" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="39" t="s">
+      <c r="C9" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="37" t="s">
+      <c r="D9" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="E9" s="37" t="s">
+      <c r="E9" s="35" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="39" t="s">
+      <c r="B10" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="39" t="s">
+      <c r="C10" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="37" t="s">
+      <c r="D10" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="E10" s="37" t="s">
+      <c r="E10" s="35" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B11" s="39" t="s">
+      <c r="B11" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="39" t="s">
+      <c r="C11" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="37" t="s">
+      <c r="D11" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="E11" s="37" t="s">
+      <c r="E11" s="35" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B12" s="39" t="s">
+      <c r="B12" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="39" t="s">
+      <c r="C12" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="37" t="s">
+      <c r="D12" s="35" t="s">
         <v>39</v>
       </c>
-      <c r="E12" s="37" t="s">
+      <c r="E12" s="35" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="39" t="s">
+      <c r="B13" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="39" t="s">
+      <c r="C13" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="37" t="s">
+      <c r="D13" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="E13" s="37" t="s">
+      <c r="E13" s="35" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B14" s="39" t="s">
+      <c r="B14" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="39" t="s">
+      <c r="C14" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="37" t="s">
+      <c r="D14" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="E14" s="37" t="s">
+      <c r="E14" s="35" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B15" s="39" t="s">
+      <c r="B15" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="39" t="s">
+      <c r="C15" s="37" t="s">
         <v>29</v>
       </c>
-      <c r="D15" s="37" t="s">
+      <c r="D15" s="35" t="s">
         <v>42</v>
       </c>
-      <c r="E15" s="37" t="s">
+      <c r="E15" s="35" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B16" s="39" t="s">
+      <c r="B16" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="39" t="s">
+      <c r="C16" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="37" t="s">
+      <c r="D16" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="E16" s="37" t="s">
+      <c r="E16" s="35" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B17" s="39" t="s">
+      <c r="B17" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="39" t="s">
+      <c r="C17" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="D17" s="37" t="s">
+      <c r="D17" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="E17" s="37" t="s">
+      <c r="E17" s="35" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
       <c r="D18" t="s">
         <v>45</v>
       </c>
-      <c r="E18" s="37" t="s">
+      <c r="E18" s="35" t="s">
         <v>33</v>
       </c>
     </row>

--- a/25MMS4124-CISCO-US-Attendance Roster_Splunk Intermediate_10th to 12th Dec.xlsx
+++ b/25MMS4124-CISCO-US-Attendance Roster_Splunk Intermediate_10th to 12th Dec.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\VK_GIT\SPLK_CISCO_10_12_2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B5FC495-8B8B-4526-9620-945C48B607E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFFE3470-476F-4E99-81A8-2F73B63D1D1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="51">
   <si>
     <t>Start Date</t>
   </si>
@@ -173,13 +173,19 @@
   </si>
   <si>
     <t>URL - https://cloud.cdp.rpsconsulting.in/</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>A</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -221,6 +227,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -475,10 +489,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -588,8 +603,12 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -977,9 +996,15 @@
       <c r="B12" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="23"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="25"/>
+      <c r="C12" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="E12" s="25" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="13" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="26" t="s">
@@ -988,9 +1013,15 @@
       <c r="B13" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="28"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="30"/>
+      <c r="C13" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="E13" s="30" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="14" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="31" t="s">
@@ -999,9 +1030,15 @@
       <c r="B14" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="19"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="14"/>
+      <c r="C14" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="15" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="26" t="s">
@@ -1010,20 +1047,32 @@
       <c r="B15" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="28"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="30"/>
+      <c r="C15" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="E15" s="30" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="16" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="32" t="s">
+      <c r="B16" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="19"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="14"/>
+      <c r="C16" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="17" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="26" t="s">
@@ -1032,9 +1081,15 @@
       <c r="B17" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="28"/>
-      <c r="D17" s="29"/>
-      <c r="E17" s="30"/>
+      <c r="C17" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="E17" s="30" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="18" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="31" t="s">
@@ -1043,9 +1098,15 @@
       <c r="B18" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="C18" s="19"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="14"/>
+      <c r="C18" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="E18" s="14" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="19" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="26" t="s">
@@ -1054,9 +1115,15 @@
       <c r="B19" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="C19" s="28"/>
-      <c r="D19" s="29"/>
-      <c r="E19" s="30"/>
+      <c r="C19" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="D19" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="E19" s="30" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="20" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="31" t="s">
@@ -1065,9 +1132,15 @@
       <c r="B20" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="C20" s="19"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="14"/>
+      <c r="C20" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="21" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="26" t="s">
@@ -1076,9 +1149,15 @@
       <c r="B21" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="C21" s="28"/>
-      <c r="D21" s="29"/>
-      <c r="E21" s="30"/>
+      <c r="C21" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="D21" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="E21" s="30" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="22" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="31" t="s">
@@ -1087,9 +1166,15 @@
       <c r="B22" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="C22" s="19"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="14"/>
+      <c r="C22" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="E22" s="14" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="23" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="26" t="s">
@@ -1098,14 +1183,23 @@
       <c r="B23" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="C23" s="28"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="30"/>
+      <c r="C23" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="D23" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="E23" s="30" t="s">
+        <v>49</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B1:C1"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="B16" r:id="rId1" xr:uid="{F9EE7A5F-D170-4EE9-886D-59C0A621B278}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
     <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;8&amp;K000000 General - RPS Data</oddFooter>
